--- a/Sensitivity_sigmaI_Plane.xlsx
+++ b/Sensitivity_sigmaI_Plane.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C666B5-2618-4CCC-B88B-584D0634296D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D6F2962-4C5A-4818-A2B5-7D4B0E6B53DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FA31995C-05AE-47D3-B23A-103621EBAF25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EA3B1C15-C0E2-488F-9979-C84AF85B144E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -418,7 +421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C2D8FA-2BBC-4731-803C-333589700E04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52FD4D8D-7A3A-4BED-BE83-D128DE74B9B5}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -509,7 +512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968728FD-FD44-42A8-A88A-19529E496913}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86107ED4-41DC-4B84-8D4B-26115A8CD5E7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -518,7 +521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301AEE45-7254-40A6-B10C-23EBB5C0B524}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E70F30-4AA1-403B-A8FA-14010392219E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
